--- a/CfdApi_0417.xlsx
+++ b/CfdApi_0417.xlsx
@@ -1,42 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Xuhua\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git_XuhuaRepo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82E9A4A4-6408-4427-B402-42B53B40DAF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3AE4B2A-F23E-4DBA-892F-D4950334AE18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9F3751C1-6DE8-429C-A8D7-F6DCAB919185}"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="1" xr2:uid="{9F3751C1-6DE8-429C-A8D7-F6DCAB919185}"/>
   </bookViews>
   <sheets>
     <sheet name="CFD_Automation" sheetId="1" r:id="rId1"/>
+    <sheet name="Process" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="102">
   <si>
     <t>connectCFD( )</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -183,166 +173,6 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">setDevicePath( </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="5"/>
-        <rFont val="Microsoft YaHei Light"/>
-        <family val="2"/>
-      </rPr>
-      <t>searchPathes.Device</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei Light"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> ) </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="5"/>
-        <rFont val="Microsoft YaHei Light"/>
-        <family val="2"/>
-      </rPr>
-      <t>'D:\BMW_GIT\IPM_HIL_Pxx\work\CFD_Projekte\CFD_Hardware'</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">setWorkingViewPath( </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="5"/>
-        <rFont val="Microsoft YaHei Light"/>
-        <family val="2"/>
-      </rPr>
-      <t>searchPathes.WorkingView</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei Light"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> ) </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="5"/>
-        <rFont val="Microsoft YaHei Light"/>
-        <family val="2"/>
-      </rPr>
-      <t>'D:\BMW_GIT\IPM_HIL_Pxx\work\CFD_Projekte\CFD_WorkingView'</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">setHWPath( </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="5"/>
-        <rFont val="Microsoft YaHei Light"/>
-        <family val="2"/>
-      </rPr>
-      <t>searchPathes.Hardware</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei Light"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> ) </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="5"/>
-        <rFont val="Microsoft YaHei Light"/>
-        <family val="2"/>
-      </rPr>
-      <t>'D:\BMW_GIT\IPM_HIL_Pxx\work\CFD_Projekte\CFD_Hardware'</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">setApplicationPath( </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="5"/>
-        <rFont val="Microsoft YaHei Light"/>
-        <family val="2"/>
-      </rPr>
-      <t>searchPathes.Anwendung</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei Light"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> )</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="5"/>
-        <rFont val="Microsoft YaHei Light"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 'D:\BMW_GIT\IPM_HIL_Pxx\work\CFD_Projekte\CFD_Anwendung'</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">setProjectPath( </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="5"/>
-        <rFont val="Microsoft YaHei Light"/>
-        <family val="2"/>
-      </rPr>
-      <t>searchPathes.Project</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei Light"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> )</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="5"/>
-        <rFont val="Microsoft YaHei Light"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 'D:\BMW_GIT\IPM_HIL_Pxx\work\CFD_Projekte'</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <t xml:space="preserve">openProject( </t>
     </r>
     <r>
@@ -376,43 +206,6 @@
   <si>
     <t>obj.ActAppl.Algorithms.ExportConflictsToXML( xmlTemporaryFile )
 [ nConflicts, conflicts ] = parseConflicts( xmlTemporaryFile )</t>
-  </si>
-  <si>
-    <r>
-      <t>cache_dir = obj.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Microsoft JhengHei UI Light"/>
-        <family val="2"/>
-      </rPr>
-      <t>ActCFD</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei UI Light"/>
-        <family val="2"/>
-      </rPr>
-      <t>.GetCustomInformation({'ApplicationCacheDirectory'})
-cfd_proj_dir = fullfile( cache_dir{1}, 'Components' )
-copyfile( fullfile( obj.SeSt_Info.cfdBuildPath, mdl{1}), fullfile( cfd_proj_dir,  mdl{1} )
-SetSimulationStatus(sub_model, 'cfd_analyse')
-simout = dsmips_configurationdesk('AddModelToCurrentProject', 'eth', true, '', false);
-obj.getallModelPortBlocks( )
-ObjRoot = obj.ModelTopology
-cfdObjName = obj.getContains( ObjRoot )
-CfdObj_temp = ObjRoot.Item( cfdObjName{ countElements } )
-if strcmpi( CfdObj_temp.Roles.Item( countRoles ) , 'ModelPortBlock' ) isMdlPotBlk = 1
-if isMdlPotBlk
-    cfdMdlPotBlks(end+1).Name = cfdObjName{ countElements }
-    cfdMdlPotBlks(end).Obj    = ObjRoot.Item( cfdObjName{ countElements } )
-    cfdMdlPotBlks(end).Root   = mdlRoot
-obj.ActMdlPotBlks = cfdMdlPotBlks</t>
-    </r>
   </si>
   <si>
     <t>actMdlPotBlk = obj.ActMdlPotBlks(:)'
@@ -625,1338 +418,6 @@
       <t xml:space="preserve"> 'D:\BMW_GIT\IPM_HIL_Pxx\work\Anwendung\CCU110G_C2_TEE1_IPF_IPB'</t>
     </r>
     <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">CFDAutomation.configure_bm_cfd() -&gt; self.create_bm_config()
-hil = self._cfd_config.get("hil") </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="5"/>
-        <rFont val="Microsoft JhengHei UI Light"/>
-        <family val="2"/>
-      </rPr>
-      <t>"PST_SYS_EE25"</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei UI Light"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-for (name, variant), (revision, core, bu_type) in self._bm_baseunits.items(): </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="5"/>
-        <rFont val="Microsoft JhengHei UI Light"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">bu_type=="BM" bu:CAN/LIN_IPB/IPF_#
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Microsoft JhengHei UI Light"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">    wv_subpath == </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="5"/>
-        <rFont val="Microsoft JhengHei UI Light"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">"EE25"
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei UI Light"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">    read_ocrpath_in_cafx() </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="5"/>
-        <rFont val="Microsoft JhengHei UI Light"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">return hw_path,wv_path,ocr_path
-    </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Microsoft JhengHei UI Light"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">    </t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <rFont val="Microsoft JhengHei UI Light"/>
-        <family val="2"/>
-      </rPr>
-      <t>wv_path</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Microsoft JhengHei UI Light"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="5"/>
-        <rFont val="Microsoft JhengHei UI Light"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">work\BaseUnitsShadow\Git\BU\CAN_IPx\revision\EESystem25\CAN_IPx_#_EESystem25_xxKwxx_BusManager.cafx
-                       work\BaseUnit\CAN_IPx_#\EESystem25\CAN_IPx_#_EESystem25_xxKwxx_BusManager.cafx
-        </t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei UI Light"/>
-        <family val="2"/>
-      </rPr>
-      <t>hw_path</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei UI Light"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="5"/>
-        <rFont val="Microsoft JhengHei UI Light"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">work\CFD_Projekte\CFD_WorkingView\BM_HW_Configurations\PST_SYS_EE25_CAN_IPx_#.cafx
-        </t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei UI Light"/>
-        <family val="2"/>
-      </rPr>
-      <t>ocr_paths:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei UI Light"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> root = ET.parse(</t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei UI Light"/>
-        <family val="2"/>
-      </rPr>
-      <t>wv_path</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei UI Light"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">) 
-                     nodes = root.findall('.//Entity[@type="ComMatrixCommunicationMatrix"]')
-                     com_mats: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="5"/>
-        <rFont val="Microsoft JhengHei UI Light"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">work\Dat_Com\CAN\DBC\EESystem25_xxKWxx\CAN_FD_IPx_#\BusDescription_EESystem25_xxKWxx_.arxml
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Microsoft JhengHei UI Light"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">    for ocr_path in </t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <rFont val="Microsoft JhengHei UI Light"/>
-        <family val="2"/>
-      </rPr>
-      <t>ocr_paths</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Microsoft JhengHei UI Light"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="5"/>
-        <rFont val="Microsoft JhengHei UI Light"/>
-        <family val="2"/>
-      </rPr>
-      <t>com_mats</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Microsoft JhengHei UI Light"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-        self.bus_manager.Configure('AddCommunicationMatrix', [ocr_path])
-    self.__import_bus_workingviews(name, wv_paths)
-        self.workingviews.Add(path, name)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="5"/>
-        <rFont val="Microsoft JhengHei UI Light"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">"CAN_IPx_#"
-        </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Microsoft JhengHei UI Light"/>
-        <family val="2"/>
-      </rPr>
-      <t>for cafx in cafxs:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="5"/>
-        <rFont val="Microsoft JhengHei UI Light"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> wv_paths:</t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color theme="5"/>
-        <rFont val="Microsoft JhengHei UI Light"/>
-        <family val="2"/>
-      </rPr>
-      <t>wv_path</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="5"/>
-        <rFont val="Microsoft JhengHei UI Light"/>
-        <family val="2"/>
-      </rPr>
-      <t>,</t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color theme="5"/>
-        <rFont val="Microsoft JhengHei UI Light"/>
-        <family val="2"/>
-      </rPr>
-      <t>hw_path</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Microsoft JhengHei UI Light"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-             self.current_workingview.Import(cafx, mode)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei UI Light"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="Microsoft JhengHei UI Light"/>
-        <family val="2"/>
-      </rPr>
-      <t>Mode = 0: Add / 1: Merge/ 2: Replace</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei UI Light"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 
-              </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="5"/>
-        <rFont val="Microsoft JhengHei UI Light"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">CAN_IPx_#_Config-&gt;BusManager, CAN_IPx_#-&gt;HW
-   </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei UI Light"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> if 'A_FlexRay' in name and 'EESystem25' in variant:
-        self.__connect_flex_fp()
-             flx_board = self.__get_device(self.hardware_topology, 'FlexRay Board')
-             flx_bus = flx_board[0] </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="5"/>
-        <rFont val="Microsoft JhengHei UI Light"/>
-        <family val="2"/>
-      </rPr>
-      <t>DS6311 FlexrayBoard(Slot18) FlexRay2 channel1-4</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei UI Light"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-                  for fid in (1,2,3,4):
-                       ctr = self.current_workingview.Item(f'FR CTR{fid}') </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="5"/>
-        <rFont val="Microsoft JhengHei UI Light"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">'FR CTR#'
-                       </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Microsoft JhengHei UI Light"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">self.algorithms.AssignChannelSet(ctr, flx_bus, True) </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="5"/>
-        <rFont val="Microsoft JhengHei UI Light"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">'Hardware Assignment 'FlexRay Function &lt;-&gt; FlexRay Board </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">set_model_path(self._cfd_config.get("app_dir")) </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Microsoft YaHei Light"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">modelpath: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="5"/>
-        <rFont val="Microsoft YaHei Light"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>work\Anwendung\CCU110G_C2_TEE1_IPF_IPB</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei Light"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-self.set_project(self._cfd_config.get("cfd_proj")  
-    </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Microsoft YaHei Light"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>projectpath:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="5"/>
-        <rFont val="Microsoft YaHei Light"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> work\CFD_Projekte\CFD_Projekt</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Microsoft YaHei Light"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="5"/>
-        <rFont val="Microsoft YaHei Light"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei Light"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">__prj_root_path: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="5"/>
-        <rFont val="Microsoft YaHei Light"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>work\CFD_Projekte</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Microsoft YaHei Light"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="5"/>
-        <rFont val="Microsoft YaHei Light"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Microsoft YaHei Light"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">__cfd_project: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="5"/>
-        <rFont val="Microsoft YaHei Light"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>CFD_Projekt</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei Light"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Microsoft YaHei Light"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">    cleanup_project()??
-    </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei Light"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>self.active_project.Open(False) -&gt; @</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF7030A0"/>
-        <rFont val="Microsoft YaHei Light"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>property</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei Light"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> active_project -&gt; @</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF7030A0"/>
-        <rFont val="Microsoft YaHei Light"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>property</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei Light"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> active_project_root -&gt; @</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF7030A0"/>
-        <rFont val="Microsoft YaHei Light"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>property</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei Light"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> app</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei Light"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-    </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei Light"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>active_project</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei Light"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> self.__active_proj = self.</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei Light"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>active_project_root</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei Light"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">.Projects.Item(self.__cfd_project) </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="5"/>
-        <rFont val="Microsoft YaHei Light"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>CFD_Projekt</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei Light"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-    </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei Light"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>active_project_root</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei Light"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> self.__active_proj_root = self.</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei Light"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>app</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei Light"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">.ProjectRoots.Item(str(self.__prj_root_path)) </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="5"/>
-        <rFont val="Microsoft YaHei Light"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">work\CFD_Projekte </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Microsoft YaHei Light"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">self.__active_proj_root.Activate()
-    </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Microsoft YaHei Light"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">app </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Microsoft YaHei Light"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>self.__reconnect(True)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei Light"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei Light"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>self.__app_object = Dispatch("ConfigurationDesk.Application")</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei Light"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-self.open_application(self._cfd_config.get("cfd_appl"))  </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="5"/>
-        <rFont val="Microsoft YaHei Light"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>PST_SYS_EE25_NA5BEV_ECAT_V7_BM_6_core.txt</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei Light"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-    __open_appl_by_file('</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="5"/>
-        <rFont val="Microsoft YaHei Light"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>PST_SYS_EE25_NA5BEV_ECAT_V7_BM_6_core.txt</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei Light"/>
-        <family val="2"/>
-      </rPr>
-      <t>')
-        self.__cfd_application_content(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="5"/>
-        <rFont val="Microsoft YaHei Light"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>'PST_SYS_EE25_NA5BEV_ECAT_V7_BM_6_core.txt'</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei Light"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">) content["template"] = self.__appl_template </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="5"/>
-        <rFont val="Microsoft YaHei Light"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>Template_PST_MiniE_ECAT_EE25_V5</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Microsoft YaHei Light"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
-        __open_application(self.__appl_template[0]) </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="5"/>
-        <rFont val="Microsoft YaHei Light"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>Template_PST_MiniE_ECAT_EE25_V5</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Microsoft YaHei Light"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
-            appl = self.project_applications.Item('</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="5"/>
-        <rFont val="Microsoft YaHei Light"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>Template_PST_MiniE_ECAT_EE25_V5</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Microsoft YaHei Light"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">') appl.Activate(False) self.__appl_name = </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="5"/>
-        <rFont val="Microsoft YaHei Light"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">Template_PST_MiniE_ECAT_EE25_V5
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei Light"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">    </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Microsoft YaHei Light"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">self.save_application_as("ipm_hil")???
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Microsoft YaHei Light"/>
-        <family val="2"/>
-      </rPr>
-      <t>cleanup_cfd_model()
-    temp_wv = active_app.WorkingViews.Add(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="5"/>
-        <rFont val="Microsoft YaHei Light"/>
-        <family val="2"/>
-      </rPr>
-      <t>'TemplateItems'</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Microsoft YaHei Light"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">), </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei Light"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">global_wv = active_app.WorkingViews.Item(0) </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="5"/>
-        <rFont val="Microsoft YaHei Light"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">‘Global’ 
-    </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Microsoft YaHei Light"/>
-        <family val="2"/>
-      </rPr>
-      <t>block_type == "</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="5"/>
-        <rFont val="Microsoft YaHei Light"/>
-        <family val="2"/>
-      </rPr>
-      <t>FB EtherCAT Slave</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Microsoft YaHei Light"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">" esipath = </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="5"/>
-        <rFont val="Microsoft YaHei Light"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">C:\Users\EXT_XU~1\AppData\Local\Temp\ECat_Slave_Interface_EE25_V7.xml
-        </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Microsoft YaHei Light"/>
-        <family val="2"/>
-      </rPr>
-      <t>Item("</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="5"/>
-        <rFont val="Microsoft YaHei Light"/>
-        <family val="2"/>
-      </rPr>
-      <t>Export ESI file</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Microsoft YaHei Light"/>
-        <family val="2"/>
-      </rPr>
-      <t>").Value</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="5"/>
-        <rFont val="Microsoft YaHei Light"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> = </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Microsoft YaHei Light"/>
-        <family val="2"/>
-      </rPr>
-      <t>esipath Item("</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="5"/>
-        <rFont val="Microsoft YaHei Light"/>
-        <family val="2"/>
-      </rPr>
-      <t>Import ESI file</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Microsoft YaHei Light"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">").Value = esipath
-    active_app.Algorithms.DeleteCompletely(models), models= [model_topology.Item(i)] </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="Microsoft YaHei Light"/>
-        <family val="2"/>
-      </rPr>
-      <t>Delete ModelTopology</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Microsoft YaHei Light"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-    atm_rel = active_app.Relations.Item('ApplicationConfiguration'), atm_rel.RemoveElements(exec_app, elements) </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="Microsoft YaHei Light"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Delete Task
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Microsoft YaHei Light"/>
-        <family val="2"/>
-      </rPr>
-      <t>self.assemble_cfd_application()</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei Light"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-    self.__appl_hardware = '</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="5"/>
-        <rFont val="Microsoft YaHei Light"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">PST_SYS_EE25_6_core.htfx' </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Microsoft YaHei Light"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">self.path_hardware= </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="5"/>
-        <rFont val="Microsoft YaHei Light"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">work\CFD_Projekte\CFD_HW\PST_SYS_EE25_6_core.htfx 
-    </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Microsoft YaHei Light"/>
-        <family val="2"/>
-      </rPr>
-      <t>self.hardware_topology.Configure("Create", params), params=[__appl_hardware, path_hardware]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei Light"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-    </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Microsoft YaHei Light"/>
-        <family val="2"/>
-      </rPr>
-      <t>self.__import_appl_workingviews()</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei Light"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-        __appl_workingviews </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="5"/>
-        <rFont val="Microsoft YaHei Light"/>
-        <family val="2"/>
-      </rPr>
-      <t>PST_SYS_EE25</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="5"/>
-        <rFont val="Microsoft YaHei Light"/>
-        <family val="2"/>
-      </rPr>
-      <t>\PST_SYS_EE25_HIL.cafx, PST_SYS_EE25_IPF.cafx, PST_SYS_EE25_IPB.cafx, PST_SYS_EE25_DS6333_M4_Config.cafx</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei Light"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-        self.workingviews.Add(path, name)
-        self.current_workingview.Import(cafx, 1)
-    self.__merge_devices()
-        __appl_devices </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="5"/>
-        <rFont val="Microsoft YaHei Light"/>
-        <family val="2"/>
-      </rPr>
-      <t>HVL\CCU_C_Muster.dtfx, HIL\LL_SYS_SX.dtfx</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei Light"/>
-        <family val="2"/>
-      </rPr>
-      <t>,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="5"/>
-        <rFont val="Microsoft YaHei Light"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei Light"/>
-        <family val="2"/>
-      </rPr>
-      <t>dtfx</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="5"/>
-        <rFont val="Microsoft YaHei Light"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">=“work\CFD_Projekte\CFD_Device”
-        </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei Light"/>
-        <family val="2"/>
-      </rPr>
-      <t>self.device_topology.Configure("Add", params) params=__appl_devices</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="5"/>
-        <rFont val="Microsoft YaHei Light"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-        </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">
-obj.</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF3399"/>
-        <rFont val="Microsoft JhengHei UI Light"/>
-        <family val="2"/>
-      </rPr>
-      <t>runPythonObjectMethod</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei UI Light"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">('InitializeCFD')
-obj.ActAppl = obj.ActProject.ActiveApplication
-obj.DeviceTopology     = obj.ActAppl.Components.Item('DeviceTopology')
-obj.FunctionTopology   = obj.ActAppl.Components.Item('IOFunctionLib')
-obj.FunctionLib        = obj.FunctionTopology.Item('Function Library')
-obj.ModelTopology      = obj.ActAppl.Components.Item('ModelTopology')
-obj.HardwareTopology   = obj.ActAppl.Components.Item('HardwareTopology')
-obj.WorkingViews       = obj.ActAppl.WorkingViews
-obj.WorkingViewsGlobal = obj.WorkingViews.Item('Global')
-obj.ATMRelation           = obj.ActAppl.Relations.Item('ApplicationConfiguration')
-</t>
-    </r>
   </si>
   <si>
     <r>
@@ -2904,106 +1365,6 @@
         <family val="2"/>
       </rPr>
       <t>Task -&gt; 'eng'</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">obj.ActAppl = appl.Activate
-obj.ATMRelation = obj.ActAppl.Relations.Item('ApplicationConfiguration')
-ExecApp = obj.ATMRelation.GetTopNodes().Item(int32(0))
-ExecApp.CreateChild(ExecApp.DataObjectTypes.Item(uint32(0)),'ProcessingUnitApplication')
-ProcUnitApp = obj.ATMRelation.GetElements(ExecApp).Item(int32(0))
-For 1:5 
-    applProcName = obj.modelNames{ 1:5 } </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="5"/>
-        <rFont val="Microsoft JhengHei UI Light"/>
-        <family val="2"/>
-      </rPr>
-      <t>eng,rbs,Mega,flx,eth</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei UI Light"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-    AppProc = ProcUnitApp.CreateChild(ProcUnitApp.DataObjectTypes.Item(uint32(0)),applProcName) </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="5"/>
-        <rFont val="Microsoft JhengHei UI Light"/>
-        <family val="2"/>
-      </rPr>
-      <t>Task 'eng''rbs'...</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei UI Light"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-    CfdModel = obj.ModelTopology.Item( applProcName )
-    obj.ATMRelation.AddElements( AppProc, {CfdModel},{} )</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="Microsoft JhengHei UI Light"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> Model &lt;-&gt; Task == Assign Model
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Microsoft JhengHei UI Light"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">    cfdType = obj.ATMRelation.GetCreatableTypes(AppProc).Item(uint32(0)) </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="5"/>
-        <rFont val="Microsoft JhengHei UI Light"/>
-        <family val="2"/>
-      </rPr>
-      <t>'Task'</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Microsoft JhengHei UI Light"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-        cfdTask      = obj.ATMRelation.CreateDataObject(cfdType, AppProc)
-        cfdTask.Name = 'Periodic Task 1'
-    timerEvent = cfdTask.CreateChild(cfdTask.DataObjectType.Item(uint32(0)),'Timer Event [Periodic Task 1]')</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei UI Light"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-    runnableFunction = obj.ATMRelation.GetElements(CfdModel).Item('Runnable Function 1 [Periodic Task 1]')
-    obj.ATMRelation.AddElements( cfdTask, { runnableFunction },{ } )
-    timerEvent.Properties.Item('Period').Value = runnableFunction.Properties.Item('Period').Value</t>
     </r>
   </si>
   <si>
@@ -3236,216 +1597,6 @@
   </si>
   <si>
     <r>
-      <t>obj.ATMRelation = obj.ActAppl.Relations.Item('ApplicationConfiguration')
-ExecApp = obj.ATMRelation.GetTopNodes().Item(int32(0))
-ProcUnitApp = obj.ATMRelation.GetElements( ExecApp ).Item(int32(0))
-for 1:5
-    ApplProc = ProcUnitApp.Item( applProcName{1} )</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="5"/>
-        <rFont val="Microsoft JhengHei UI Light"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 'eng''rbs''Mega''eth''flx'
-   </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Microsoft JhengHei UI Light"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> CfdModel = obj.ModelTopology.Item( applProcName{1} )</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei UI Light"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-    modelElements = obj.ATMRelation.GetElements( CfdModel ) </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="5"/>
-        <rFont val="Microsoft JhengHei UI Light"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">'Runnable Function 1 [Periodic Task 1]'
-         </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Microsoft JhengHei UI Light"/>
-        <family val="2"/>
-      </rPr>
-      <t>for taskDefintion = defineTask(:)'</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="5"/>
-        <rFont val="Microsoft JhengHei UI Light"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> Name RTTEnable nOverruns Prio DAQRaster RunFunction</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Microsoft JhengHei UI Light"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-            CfdTask = ApplProc.Item( taskDefintion.Name ) </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="5"/>
-        <rFont val="Microsoft JhengHei UI Light"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">''Periodic Task 1''
-            </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Microsoft JhengHei UI Light"/>
-        <family val="2"/>
-      </rPr>
-      <t>sampleTime     = CfdTask.Item( taskDefintion.RunFunction ).Properties.Item('Period').Value</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="5"/>
-        <rFont val="Microsoft JhengHei UI Light"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 0.001s</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Microsoft JhengHei UI Light"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-                                                         </t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <rFont val="Microsoft JhengHei UI Light"/>
-        <family val="2"/>
-      </rPr>
-      <t>taskDefintion.RunFunction</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Microsoft JhengHei UI Light"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="5"/>
-        <rFont val="Microsoft JhengHei UI Light"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">'Runnable Function 1 [Periodic Task 1]'
-            </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Microsoft JhengHei UI Light"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">DAQRaster_Name = [ taskDefintion.DAQRaster ' [' num2str( sampleTime , '%10.3e s' ) ']' ] </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="5"/>
-        <rFont val="Microsoft JhengHei UI Light"/>
-        <family val="2"/>
-      </rPr>
-      <t>'Runnable Function 1 [Periodic Task 1]'</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei UI Light"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-            CfdTask.Properties.Item('IsRealTimeTestingEnabled').Value = taskDefintion.RTTEnabled' </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="5"/>
-        <rFont val="Microsoft JhengHei UI Light"/>
-        <family val="2"/>
-      </rPr>
-      <t>0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei UI Light"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-            CfdTask.Properties.Item('NumberOfAcceptedOverruns').Value = taskDefintion.nOverruns </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="5"/>
-        <rFont val="Microsoft JhengHei UI Light"/>
-        <family val="2"/>
-      </rPr>
-      <t>-1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei UI Light"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-            CfdTask.Properties.Item('Priority').Value = taskDefintion.Prio </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="5"/>
-        <rFont val="Microsoft JhengHei UI Light"/>
-        <family val="2"/>
-      </rPr>
-      <t>58</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <rPr>
         <b/>
         <sz val="11"/>
@@ -3738,415 +1889,6 @@
   </si>
   <si>
     <t>configBuildConfigurationSet( myProject.is_busmanager, CFD.Model.FMU, CFD.Data.TargetArchitecture, CFD.Data.compile_debug )</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Microsoft JhengHei UI Light"/>
-        <family val="2"/>
-      </rPr>
-      <t>self.link()</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei UI Light"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-    for _bm_baseunits.items():
-        self.busconfig_names '</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="5"/>
-        <rFont val="Microsoft JhengHei UI Light"/>
-        <family val="2"/>
-      </rPr>
-      <t>CAN_IPB_1_config</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei UI Light"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">'
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Microsoft JhengHei UI Light"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">            for topology in self.model_topology: 
-                if self.add_model_topology(topology) &gt; 2: break 
-                    if not topology.Roles.Contains('ModelInterfaceGroup'): </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="4"/>
-        <rFont val="Microsoft JhengHei UI Light"/>
-        <family val="2"/>
-      </rPr>
-      <t>return2 不进入port层(red)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Microsoft JhengHei UI Light"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei UI Light"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">                    if topology.Name in self.current_topology_searchnames:
-                        self.current_workingview.Add(topology) </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="5"/>
-        <rFont val="Microsoft JhengHei UI Light"/>
-        <family val="2"/>
-      </rPr>
-      <t>'CAN_IPB_1_config'</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei UI Light"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-                    for next_topology in topology: 
-                        status = self.add_model_topology(next_topology) </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="4"/>
-        <rFont val="Microsoft JhengHei UI Light"/>
-        <family val="2"/>
-      </rPr>
-      <t>历遍topology</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei UI Light"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Microsoft JhengHei UI Light"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">        self._connect_busmanager_blocks()
-            function_block = self.find_port_block() </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="5"/>
-        <rFont val="Microsoft JhengHei UI Light"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">CAN_IPB_1_config
-            </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Microsoft JhengHei UI Light"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">modelport_block_in = self.find_port_block('_In') </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="5"/>
-        <rFont val="Microsoft JhengHei UI Light"/>
-        <family val="2"/>
-      </rPr>
-      <t>CAN_IPB_1_config_In</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Microsoft JhengHei UI Light"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="5"/>
-        <rFont val="Microsoft JhengHei UI Light"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">            </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Microsoft JhengHei UI Light"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">modelport_block_out = self.find_port_block('_Out')  </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="5"/>
-        <rFont val="Microsoft JhengHei UI Light"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">CAN_IPB_1_config_Out
-           </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Microsoft JhengHei UI Light"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> conn_in = </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="4"/>
-        <rFont val="Microsoft JhengHei UI Light"/>
-        <family val="2"/>
-      </rPr>
-      <t>返回connect的count值</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Microsoft JhengHei UI Light"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> self.algorithms.</t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <rFont val="Microsoft JhengHei UI Light"/>
-        <family val="2"/>
-      </rPr>
-      <t>ConnectObjectsAutomatically</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Microsoft JhengHei UI Light"/>
-        <family val="2"/>
-      </rPr>
-      <t>(function_block,modelport_block_in)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei UI Light"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-            conn_out = </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="4"/>
-        <rFont val="Microsoft JhengHei UI Light"/>
-        <family val="2"/>
-      </rPr>
-      <t>返回connect的count值</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei UI Light"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> self.algorithms.</t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei UI Light"/>
-        <family val="2"/>
-      </rPr>
-      <t>ConnectObjectsAutomatically</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei UI Light"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">(function_block,modelport_block_out)
-            self.check_block_connections(function_block, True)
-            self.check_block_connections(modelport_block_in)
-            self.check_block_connections(modelport_block_out)
-                 for child in block: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="4"/>
-        <rFont val="Microsoft JhengHei UI Light"/>
-        <family val="2"/>
-      </rPr>
-      <t>function最外层的block</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei UI Light"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-                    self</t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei UI Light"/>
-        <family val="2"/>
-      </rPr>
-      <t>.check_block_connections</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei UI Light"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">(child, is_functionblock, path) </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="4"/>
-        <rFont val="Microsoft JhengHei UI Light"/>
-        <family val="2"/>
-      </rPr>
-      <t>历遍子项</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei UI Light"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-                        if block.Item(0).GetCount():  </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="4"/>
-        <rFont val="Microsoft JhengHei UI Light"/>
-        <family val="2"/>
-      </rPr>
-      <t>无子项的最终port</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei UI Light"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-                            for child in block:
-                                self</t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei UI Light"/>
-        <family val="2"/>
-      </rPr>
-      <t>.check_block_connections</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei UI Light"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">(child, is_functionblock, path)
-                                    if child.ConnectedObjects.Count == 0 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="4"/>
-        <rFont val="Microsoft JhengHei UI Light"/>
-        <family val="2"/>
-      </rPr>
-      <t>无连接判断</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Microsoft JhengHei UI Light"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-                                        if child.IsOfRole('EventPort'):
-                                            self.missing_connections.append(f'{path}{child.Name}')
-                                        elif child.Properties.Item('IsMappable').Value:
-                                            self.missing_connections.append(f'{path}{child.Name}')</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei UI Light"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">        </t>
-    </r>
   </si>
   <si>
     <r>
@@ -6517,23 +4259,2522 @@
       <t>table</t>
     </r>
   </si>
+  <si>
+    <t>IO cafx</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SimulinkModel</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>InterCpu</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">CFDAutomation.configure_bm_cfd() -&gt; self.create_bm_config()
+hil = self._cfd_config.get("hil") </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="5"/>
+        <rFont val="Microsoft JhengHei UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t>"PST_SYS_EE25"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+for (name, variant), (revision, core, bu_type) in self._bm_baseunits.items(): </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="5"/>
+        <rFont val="Microsoft JhengHei UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">bu_type=="BM" bu:CAN/LIN_IPB/IPF_#
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft JhengHei UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">    wv_subpath == </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="5"/>
+        <rFont val="Microsoft JhengHei UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">"EE25"
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">    read_ocrpath_in_cafx() </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="5"/>
+        <rFont val="Microsoft JhengHei UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">return hw_path,wv_path,ocr_path
+    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft JhengHei UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <rFont val="Microsoft JhengHei UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t>wv_path</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft JhengHei UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="5"/>
+        <rFont val="Microsoft JhengHei UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">work\BaseUnitsShadow\Git\BU\CAN_IPx\revision\EESystem25\CAN_IPx_#_EESystem25_xxKwxx_BusManager.cafx
+                       work\BaseUnit\CAN_IPx_#\EESystem25\CAN_IPx_#_EESystem25_xxKwxx_BusManager.cafx
+        </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t>hw_path</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="5"/>
+        <rFont val="Microsoft JhengHei UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">work\CFD_Projekte\CFD_WorkingView\BM_HW_Configurations\PST_SYS_EE25_CAN_IPx_#.cafx
+        </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t>ocr_paths:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> root = ET.parse(</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t>wv_path</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">) 
+                     nodes = root.findall('.//Entity[@type="ComMatrixCommunicationMatrix"]')
+                     com_mats: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="5"/>
+        <rFont val="Microsoft JhengHei UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">work\Dat_Com\CAN\DBC\EESystem25_xxKWxx\CAN_FD_IPx_#\BusDescription_EESystem25_xxKWxx_.arxml
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft JhengHei UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">    for ocr_path in </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <rFont val="Microsoft JhengHei UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t>ocr_paths</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft JhengHei UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="5"/>
+        <rFont val="Microsoft JhengHei UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t>com_mats</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft JhengHei UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+        self.bus_manager.Configure('AddCommunicationMatrix', [ocr_path])
+    self.__import_bus_workingviews(name, wv_paths)
+        self.workingviews.Add(path, name)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="5"/>
+        <rFont val="Microsoft JhengHei UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">"CAN_IPx_#"
+        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft JhengHei UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t>for cafx in cafxs:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="5"/>
+        <rFont val="Microsoft JhengHei UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> wv_paths:</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color theme="5"/>
+        <rFont val="Microsoft JhengHei UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t>wv_path</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="5"/>
+        <rFont val="Microsoft JhengHei UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color theme="5"/>
+        <rFont val="Microsoft JhengHei UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t>hw_path</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft JhengHei UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+             self.current_workingview.Import(cafx, mode)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Microsoft JhengHei UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t>Mode = 0: Add / 1: Merge/ 2: Replace</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 
+              </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="5"/>
+        <rFont val="Microsoft JhengHei UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">CAN_IPx_#_Config-&gt;BusManager, CAN_IPx_#-&gt;HW
+   </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> if 'A_FlexRay' in name and 'EESystem25' in variant:
+        self.__connect_flex_fp()
+             flx_board = self.__get_device(self.hardware_topology, 'FlexRay Board')
+             flx_bus = flx_board[0] </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="5"/>
+        <rFont val="Microsoft JhengHei UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t>DS6311 FlexrayBoard(Slot18) FlexRay2 channel1-4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+                  for fid in (1,2,3,4):
+                       ctr = self.current_workingview.Item(f'FR CTR{fid}') </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="5"/>
+        <rFont val="Microsoft JhengHei UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">'FR CTR#'
+                       </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft JhengHei UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">self.algorithms.AssignChannelSet(ctr, flx_bus, True) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="5"/>
+        <rFont val="Microsoft JhengHei UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">'Hardware Assignment 'FlexRay Function &lt;-&gt; FlexRay Board </t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>arxml</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FlexRay Function&lt;-&gt;Hardware CTR</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>obj.ATMRelation = obj.ActAppl.Relations.Item('ApplicationConfiguration')
+ExecApp = obj.ATMRelation.GetTopNodes().Item(int32(0))
+ProcUnitApp = obj.ATMRelation.GetElements( ExecApp ).Item(int32(0))
+for 1:5
+    ApplProc = ProcUnitApp.Item( applProcName{1} )</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="5"/>
+        <rFont val="Microsoft JhengHei UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 'eng''rbs''Mega''eth''flx'
+   </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft JhengHei UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> CfdModel = obj.ModelTopology.Item( applProcName{1} )</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+    modelElements = obj.ATMRelation.GetElements( CfdModel ) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="5"/>
+        <rFont val="Microsoft JhengHei UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">'Runnable Function 1 [Periodic Task 1]'
+         </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft JhengHei UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t>for taskDefintion = defineTask(:)'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="5"/>
+        <rFont val="Microsoft JhengHei UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Name RTTEnable nOverruns Prio DAQRaster RunFunction</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft JhengHei UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+            CfdTask = ApplProc.Item( taskDefintion.Name ) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="5"/>
+        <rFont val="Microsoft JhengHei UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">''Periodic Task 1''
+            </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft JhengHei UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t>sampleTime     = CfdTask.Item( taskDefintion.RunFunction ).Properties.Item('Period').Value</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="5"/>
+        <rFont val="Microsoft JhengHei UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 0.001s</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft JhengHei UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+                                                         </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <rFont val="Microsoft JhengHei UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t>taskDefintion.RunFunction</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft JhengHei UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="5"/>
+        <rFont val="Microsoft JhengHei UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">'Runnable Function 1 [Periodic Task 1]'
+            </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft JhengHei UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">DAQRaster_Name = [ taskDefintion.DAQRaster ' [' num2str( sampleTime , '%10.3e s' ) ']' ] </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="5"/>
+        <rFont val="Microsoft JhengHei UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t>'Runnable Function 1 [Periodic Task 1]'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+            CfdTask.Properties.Item('IsRealTimeTestingEnabled').Value = taskDefintion.RTTEnabled' </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="5"/>
+        <rFont val="Microsoft JhengHei UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t>0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+            CfdTask.Properties.Item('NumberOfAcceptedOverruns').Value = taskDefintion.nOverruns </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="5"/>
+        <rFont val="Microsoft JhengHei UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t>-1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+            CfdTask.Properties.Item('Priority').Value = taskDefintion.Prio </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="5"/>
+        <rFont val="Microsoft JhengHei UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t>58</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Processors</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Processor &lt;-&gt;Model</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">obj.ActAppl = appl.Activate
+obj.ATMRelation = obj.ActAppl.Relations.Item('ApplicationConfiguration')
+ExecApp = obj.ATMRelation.GetTopNodes().Item(int32(0))
+ExecApp.CreateChild(ExecApp.DataObjectTypes.Item(uint32(0)),'ProcessingUnitApplication')
+ProcUnitApp = obj.ATMRelation.GetElements(ExecApp).Item(int32(0))
+For 1:5 
+    applProcName = obj.modelNames{ 1:5 } </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="5"/>
+        <rFont val="Microsoft JhengHei UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t>eng,rbs,Mega,flx,eth</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+    AppProc = ProcUnitApp.CreateChild(ProcUnitApp.DataObjectTypes.Item(uint32(0)),applProcName) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="5"/>
+        <rFont val="Microsoft JhengHei UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t>Task 'eng''rbs'...</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+    CfdModel = obj.ModelTopology.Item( applProcName )
+    obj.ATMRelation.AddElements( AppProc, {CfdModel},{} )</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Microsoft JhengHei UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Model &lt;-&gt; Task == Assign Model
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft JhengHei UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">    cfdType = obj.ATMRelation.GetCreatableTypes(AppProc).Item(uint32(0)) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="5"/>
+        <rFont val="Microsoft JhengHei UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t>'Task'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft JhengHei UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+        cfdTask      = obj.ATMRelation.CreateDataObject(cfdType, AppProc)
+        cfdTask.Name = 'Periodic Task 1'
+    timerEvent = cfdTask.CreateChild(cfdTask.DataObjectType.Item(uint32(0)),'Timer Event [Periodic Task 1]')</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+    runnableFunction = obj.ATMRelation.GetElements(CfdModel).Item('Runnable Function 1 [Periodic Task 1]')
+    obj.ATMRelation.AddElements( cfdTask, { runnableFunction },{ } )
+    timerEvent.Properties.Item('Period').Value = runnableFunction.Properties.Item('Period').Value</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Periodic Task &lt;-&gt; Timer Event ,Runnable Function1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Runnable Function 1 sampleTime = 0.001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Periodic Task</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NumberOfAcceptedOverruns , IsRealTimeTestingEnabled, Priority</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft JhengHei UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t>self.link()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+    for _bm_baseunits.items():
+        self.busconfig_names '</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="5"/>
+        <rFont val="Microsoft JhengHei UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t>CAN_IPB_1_config</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">'
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft JhengHei UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">            for topology in self.model_topology: 
+                if self.add_model_topology(topology) &gt; 2: break 
+                    if not topology.Roles.Contains('ModelInterfaceGroup'): </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="4"/>
+        <rFont val="Microsoft JhengHei UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t>return2 不进入port层(red)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft JhengHei UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">                    if topology.Name in self.current_topology_searchnames:
+                        self.current_workingview.Add(topology) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="5"/>
+        <rFont val="Microsoft JhengHei UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t>workingview</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="5"/>
+        <rFont val="Microsoft JhengHei UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t>add model 'CAN_IPB_1_config'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+                    for next_topology in topology: 
+                        status = self.add_model_topology(next_topology) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="4"/>
+        <rFont val="Microsoft JhengHei UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t>历遍topology</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft JhengHei UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">        self._connect_busmanager_blocks()
+            function_block = self.find_port_block() </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="5"/>
+        <rFont val="Microsoft JhengHei UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">CAN_IPB_1_config
+            </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft JhengHei UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">modelport_block_in = self.find_port_block('_In') </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="5"/>
+        <rFont val="Microsoft JhengHei UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t>CAN_IPB_1_config_In</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft JhengHei UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="5"/>
+        <rFont val="Microsoft JhengHei UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">            </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft JhengHei UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">modelport_block_out = self.find_port_block('_Out')  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="5"/>
+        <rFont val="Microsoft JhengHei UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">CAN_IPB_1_config_Out
+           </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft JhengHei UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> conn_in = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="4"/>
+        <rFont val="Microsoft JhengHei UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t>返回connect的count值</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft JhengHei UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> self.algorithms.</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <rFont val="Microsoft JhengHei UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t>ConnectObjectsAutomatically</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft JhengHei UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t>(function_block,modelport_block_in)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+            conn_out = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="4"/>
+        <rFont val="Microsoft JhengHei UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t>返回connect的count值</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> self.algorithms.</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t>ConnectObjectsAutomatically</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">(function_block,modelport_block_out)
+            self.check_block_connections(function_block, True)
+            self.check_block_connections(modelport_block_in)
+            self.check_block_connections(modelport_block_out)
+                 for child in block: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="4"/>
+        <rFont val="Microsoft JhengHei UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t>function最外层的block</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+                    self</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t>.check_block_connections</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">(child, is_functionblock, path) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="4"/>
+        <rFont val="Microsoft JhengHei UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t>历遍子项</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+                        if block.Item(0).GetCount():  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="4"/>
+        <rFont val="Microsoft JhengHei UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t>无子项的最终port</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+                            for child in block:
+                                self</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t>.check_block_connections</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">(child, is_functionblock, path)
+                                    if child.ConnectedObjects.Count == 0 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="4"/>
+        <rFont val="Microsoft JhengHei UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t>无连接判断</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft JhengHei UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+                                        if child.IsOfRole('EventPort'):
+                                            self.missing_connections.append(f'{path}{child.Name}')
+                                        elif child.Properties.Item('IsMappable').Value:
+                                            self.missing_connections.append(f'{path}{child.Name}')</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">        </t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BusManager_Config</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bus_Config function &lt;-&gt; config_in&amp;out model</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>connected count: Bus_Config function, config_in ,config_out</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">WorkingViews </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+cafx</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t>BusManager</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+arxml, cafx</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei Light"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>Hardware</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei UI Light"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t xml:space="preserve">
+htfx</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bus Task</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Overruns = -1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>cache_dir = obj.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Microsoft JhengHei UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t>ActCFD</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t>.GetCustomInformation({'ApplicationCacheDirectory'})
+cfd_proj_dir = fullfile( cache_dir{1}, 'Components' )
+copyfile( fullfile( obj.SeSt_Info.cfdBuildPath, mdl{1}), fullfile( cfd_proj_dir,  mdl{1} )
+SetSimulationStatus(sub_model, 'cfd_analyse')
+simout = dsmips_configurationdesk('AddModelToCurrentProject', 'eth', true, '', false);
+obj.getallModelPortBlocks( )
+ObjRoot = obj.ModelTopology
+cfdObjName = obj.getContains( ObjRoot )
+CfdObj_temp = ObjRoot.Item( cfdObjName{ countElements } )
+if strcmpi( CfdObj_temp.Roles.Item( countRoles ) , 'ModelPortBlock' ) isMdlPotBlk = 1
+if isMdlPotBlk
+    cfdMdlPotBlks(end+1).Name = cfdObjName{ countElements }
+    cfdMdlPotBlks(end).Obj    = ObjRoot.Item( cfdObjName{ countElements } )
+    cfdMdlPotBlks(end).Root   = mdlRoot
+obj.ActMdlPotBlks = cfdMdlPotBlks</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>analyze model</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>add model</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">setDevicePath( </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="5"/>
+        <rFont val="Microsoft YaHei Light"/>
+        <family val="2"/>
+      </rPr>
+      <t>searchPathes.Device</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei Light"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> ) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="5"/>
+        <rFont val="Microsoft YaHei Light"/>
+        <family val="2"/>
+      </rPr>
+      <t>'D:\BMW_GIT\IPM_HIL_Pxx\work\CFD_Projekte\CFD_Device'</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Path</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">setApplicationPath( </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="5"/>
+        <rFont val="Microsoft YaHei Light"/>
+        <family val="2"/>
+      </rPr>
+      <t>searchPathes.Anwendung</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei Light"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> )</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="5"/>
+        <rFont val="Microsoft YaHei Light"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 'D:\BMW_GIT\IPM_HIL_Pxx\work\CFD_Projekte\CFD_Anwendung'</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">setHWPath( </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="5"/>
+        <rFont val="Microsoft YaHei Light"/>
+        <family val="2"/>
+      </rPr>
+      <t>searchPathes.Hardware</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei Light"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> ) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="5"/>
+        <rFont val="Microsoft YaHei Light"/>
+        <family val="2"/>
+      </rPr>
+      <t>'D:\BMW_GIT\IPM_HIL_Pxx\work\CFD_Projekte\CFD_Hardware'</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">setWorkingViewPath( </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="5"/>
+        <rFont val="Microsoft YaHei Light"/>
+        <family val="2"/>
+      </rPr>
+      <t>searchPathes.WorkingView</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei Light"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> ) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="5"/>
+        <rFont val="Microsoft YaHei Light"/>
+        <family val="2"/>
+      </rPr>
+      <t>'D:\BMW_GIT\IPM_HIL_Pxx\work\CFD_Projekte\CFD_WorkingView'</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">setProjectPath( </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="5"/>
+        <rFont val="Microsoft YaHei Light"/>
+        <family val="2"/>
+      </rPr>
+      <t>searchPathes.Project</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei Light"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> )</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="5"/>
+        <rFont val="Microsoft YaHei Light"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 'D:\BMW_GIT\IPM_HIL_Pxx\work\CFD_Projekte'</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CFD_Projekte
+CFD_Anwendung
+CFD_Hardware
+CFD_WorkingView
+CFD_Device
+ModelPath</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OpenApplication</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">set_model_path(self._cfd_config.get("app_dir")) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei Light"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">modelpath: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="5"/>
+        <rFont val="Microsoft YaHei Light"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>work\Anwendung\CCU110G_C2_TEE1_IPF_IPB</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei Light"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+self.set_project(self._cfd_config.get("cfd_proj")  
+    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei Light"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>projectpath:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="5"/>
+        <rFont val="Microsoft YaHei Light"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> work\CFD_Projekte\CFD_Projekt</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei Light"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="5"/>
+        <rFont val="Microsoft YaHei Light"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei Light"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">__prj_root_path: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="5"/>
+        <rFont val="Microsoft YaHei Light"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>work\CFD_Projekte</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei Light"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="5"/>
+        <rFont val="Microsoft YaHei Light"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei Light"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">__cfd_project: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="5"/>
+        <rFont val="Microsoft YaHei Light"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>CFD_Projekt</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei Light"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Microsoft YaHei Light"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">    cleanup_project()??
+    </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei Light"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>self.active_project.Open(False) -&gt; @</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Microsoft YaHei Light"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>property</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei Light"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> active_project -&gt; @</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Microsoft YaHei Light"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>property</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei Light"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> active_project_root -&gt; @</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Microsoft YaHei Light"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>property</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei Light"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> app</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei Light"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+    </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei Light"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>active_project</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei Light"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> self.__active_proj = self.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei Light"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>active_project_root</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei Light"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">.Projects.Item(self.__cfd_project) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="5"/>
+        <rFont val="Microsoft YaHei Light"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>CFD_Projekt</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei Light"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+    </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei Light"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>active_project_root</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei Light"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> self.__active_proj_root = self.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei Light"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>app</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei Light"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">.ProjectRoots.Item(str(self.__prj_root_path)) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="5"/>
+        <rFont val="Microsoft YaHei Light"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">work\CFD_Projekte </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei Light"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">self.__active_proj_root.Activate()
+    </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei Light"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">app </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei Light"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>self.__reconnect(True)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei Light"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei Light"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>self.__app_object = Dispatch("ConfigurationDesk.Application")</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei Light"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+self.open_application(self._cfd_config.get("cfd_appl"))  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="5"/>
+        <rFont val="Microsoft YaHei Light"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>PST_SYS_EE25_NA5BEV_ECAT_V7_BM_6_core.txt</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei Light"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+    __open_appl_by_file('</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="5"/>
+        <rFont val="Microsoft YaHei Light"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>PST_SYS_EE25_NA5BEV_ECAT_V7_BM_6_core.txt</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei Light"/>
+        <family val="2"/>
+      </rPr>
+      <t>')
+        self.__cfd_application_content(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="5"/>
+        <rFont val="Microsoft YaHei Light"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>'PST_SYS_EE25_NA5BEV_ECAT_V7_BM_6_core.txt'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei Light"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">) content["template"] = self.__appl_template </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="5"/>
+        <rFont val="Microsoft YaHei Light"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Template_PST_MiniE_ECAT_EE25_V5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei Light"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+        __open_application(self.__appl_template[0]) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="5"/>
+        <rFont val="Microsoft YaHei Light"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Template_PST_MiniE_ECAT_EE25_V5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei Light"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+            appl = self.project_applications.Item('</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="5"/>
+        <rFont val="Microsoft YaHei Light"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Template_PST_MiniE_ECAT_EE25_V5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei Light"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">') appl.Activate(False) self.__appl_name = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="5"/>
+        <rFont val="Microsoft YaHei Light"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">Template_PST_MiniE_ECAT_EE25_V5
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei Light"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Microsoft YaHei Light"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">self.save_application_as("ipm_hil")???
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei Light"/>
+        <family val="2"/>
+      </rPr>
+      <t>cleanup_cfd_model()
+    temp_wv = active_app.WorkingViews.Add(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="5"/>
+        <rFont val="Microsoft YaHei Light"/>
+        <family val="2"/>
+      </rPr>
+      <t>'TemplateItems'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei Light"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">), </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei Light"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">global_wv = active_app.WorkingViews.Item(0) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="5"/>
+        <rFont val="Microsoft YaHei Light"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">‘Global’ 
+    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei Light"/>
+        <family val="2"/>
+      </rPr>
+      <t>block_type == "</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="5"/>
+        <rFont val="Microsoft YaHei Light"/>
+        <family val="2"/>
+      </rPr>
+      <t>FB EtherCAT Slave</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei Light"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">" esipath = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="5"/>
+        <rFont val="Microsoft YaHei Light"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">C:\Users\EXT_XU~1\AppData\Local\Temp\ECat_Slave_Interface_EE25_V7.xml
+        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei Light"/>
+        <family val="2"/>
+      </rPr>
+      <t>Item("</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="5"/>
+        <rFont val="Microsoft YaHei Light"/>
+        <family val="2"/>
+      </rPr>
+      <t>Export ESI file</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei Light"/>
+        <family val="2"/>
+      </rPr>
+      <t>").Value</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="5"/>
+        <rFont val="Microsoft YaHei Light"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei Light"/>
+        <family val="2"/>
+      </rPr>
+      <t>esipath Item("</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="5"/>
+        <rFont val="Microsoft YaHei Light"/>
+        <family val="2"/>
+      </rPr>
+      <t>Import ESI file</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei Light"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">").Value = esipath
+    active_app.Algorithms.DeleteCompletely(models), models= [model_topology.Item(i)] </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Microsoft YaHei Light"/>
+        <family val="2"/>
+      </rPr>
+      <t>Delete ModelTopology</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei Light"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+    atm_rel = active_app.Relations.Item('ApplicationConfiguration'), atm_rel.RemoveElements(exec_app, elements) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Microsoft YaHei Light"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Delete Task
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei Light"/>
+        <family val="2"/>
+      </rPr>
+      <t>self.assemble_cfd_application()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei Light"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+    self.__appl_hardware = '</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="5"/>
+        <rFont val="Microsoft YaHei Light"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">PST_SYS_EE25_6_core.htfx' </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei Light"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">self.path_hardware= </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="5"/>
+        <rFont val="Microsoft YaHei Light"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">work\CFD_Projekte\CFD_HW\PST_SYS_EE25_6_core.htfx 
+    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei Light"/>
+        <family val="2"/>
+      </rPr>
+      <t>self.hardware_topology.Configure("Create", params), params=[__appl_hardware, path_hardware]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei Light"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Microsoft YaHei Light"/>
+        <family val="2"/>
+      </rPr>
+      <t>self.__import_appl_workingviews()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei Light"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+        __appl_workingviews </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="5"/>
+        <rFont val="Microsoft YaHei Light"/>
+        <family val="2"/>
+      </rPr>
+      <t>PST_SYS_EE25</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="5"/>
+        <rFont val="Microsoft YaHei Light"/>
+        <family val="2"/>
+      </rPr>
+      <t>\PST_SYS_EE25_HIL.cafx, PST_SYS_EE25_IPF.cafx, PST_SYS_EE25_IPB.cafx, PST_SYS_EE25_DS6333_M4_Config.cafx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei Light"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+        self.workingviews.Add(path, name)
+        self.current_workingview.Import(cafx, 1)
+    self.__merge_devices()
+        __appl_devices </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="5"/>
+        <rFont val="Microsoft YaHei Light"/>
+        <family val="2"/>
+      </rPr>
+      <t>HVL\CCU_C_Muster.dtfx, HIL\LL_SYS_SX.dtfx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei Light"/>
+        <family val="2"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="5"/>
+        <rFont val="Microsoft YaHei Light"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei Light"/>
+        <family val="2"/>
+      </rPr>
+      <t>dtfx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="5"/>
+        <rFont val="Microsoft YaHei Light"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">=“work\CFD_Projekte\CFD_Device”
+        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei Light"/>
+        <family val="2"/>
+      </rPr>
+      <t>self.device_topology.Configure("Add", params) params=__appl_devices</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="5"/>
+        <rFont val="Microsoft YaHei Light"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+        </t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">
+obj.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF3399"/>
+        <rFont val="Microsoft JhengHei UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t>runPythonObjectMethod</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">('InitializeCFD')
+obj.ActAppl = obj.ActProject.ActiveApplication
+obj.DeviceTopology     = obj.ActAppl.Components.Item('DeviceTopology')
+obj.FunctionTopology   = obj.ActAppl.Components.Item('IOFunctionLib')
+obj.FunctionLib        = obj.FunctionTopology.Item('Function Library')
+obj.ModelTopology      = obj.ActAppl.Components.Item('ModelTopology')
+obj.HardwareTopology   = obj.ActAppl.Components.Item('HardwareTopology')
+obj.WorkingViews       = obj.ActAppl.WorkingViews
+obj.WorkingViewsGlobal = obj.WorkingViews.Item('Global')
+obj.ATMRelation           = obj.ActAppl.Relations.Item('ApplicationConfiguration')
+</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">app -&gt; active_project_root -&gt; active_project </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>app.Topology(Device, Model, Hardware, Function, FunctionLib)
+app.WorkingViews</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>ProcessingUnit</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>, LabBox</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>workingview</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t>Bus_Config</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> &amp; Bus_Hardware</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="47">
+  <fonts count="52">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -6836,6 +7077,44 @@
       <name val="Microsoft JhengHei UI Light"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Microsoft JhengHei UI Light"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Microsoft JhengHei Light"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -6887,7 +7166,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="50">
+  <borders count="57">
     <border>
       <left/>
       <right/>
@@ -7476,13 +7755,98 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="hair">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="hair">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="93">
+  <cellXfs count="118">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -7595,126 +7959,159 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="6" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="8" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="8" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="8" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="13" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="6" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="8" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="8" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="13" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="6" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="6" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="8" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="8" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="8" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="39" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -7724,45 +8121,87 @@
     <xf numFmtId="0" fontId="39" fillId="8" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="8" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="8" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="8" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="8" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="8" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="6" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="6" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="2" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="6" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -8292,8 +8731,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="25084269" y="19067694"/>
-          <a:ext cx="8297683" cy="2424291"/>
+          <a:off x="30451887" y="23017768"/>
+          <a:ext cx="9000570" cy="2427466"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -8353,8 +8792,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="25071387" y="16543338"/>
-          <a:ext cx="8242300" cy="2520417"/>
+          <a:off x="30439005" y="20493412"/>
+          <a:ext cx="8948362" cy="2517242"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -8495,8 +8934,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="19940649" y="27879799"/>
-          <a:ext cx="7594456" cy="3119745"/>
+          <a:off x="21526111" y="27777248"/>
+          <a:ext cx="8158028" cy="3122920"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -8583,8 +9022,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="17383332" y="34415144"/>
-          <a:ext cx="7712157" cy="1114652"/>
+          <a:off x="18974567" y="34304019"/>
+          <a:ext cx="8275111" cy="1117827"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -8627,8 +9066,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="16736787" y="35578143"/>
-          <a:ext cx="4154714" cy="1288536"/>
+          <a:off x="18963022" y="35469286"/>
+          <a:ext cx="4154714" cy="1285361"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -8671,8 +9110,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="20969943" y="35574942"/>
-          <a:ext cx="3570940" cy="1280513"/>
+          <a:off x="23192443" y="35466618"/>
+          <a:ext cx="4139870" cy="1280513"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -8715,8 +9154,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="29483173" y="37218629"/>
-          <a:ext cx="3196659" cy="1451427"/>
+          <a:off x="32016382" y="37108947"/>
+          <a:ext cx="3626099" cy="1451427"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -8759,8 +9198,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="20983862" y="36971844"/>
-          <a:ext cx="8470425" cy="2639786"/>
+          <a:off x="22569324" y="36862162"/>
+          <a:ext cx="9421347" cy="2636611"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -8803,7 +9242,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="23665358" y="42129363"/>
+          <a:off x="25817567" y="42015946"/>
           <a:ext cx="1570114" cy="2474026"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -8847,8 +9286,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="25262202" y="42152455"/>
-          <a:ext cx="1527479" cy="2441863"/>
+          <a:off x="27414411" y="42039038"/>
+          <a:ext cx="1530654" cy="2445038"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -8891,8 +9330,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="26833285" y="42216780"/>
-          <a:ext cx="4002149" cy="2336775"/>
+          <a:off x="28985494" y="42103363"/>
+          <a:ext cx="4552934" cy="2339950"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -8906,13 +9345,13 @@
       <xdr:col>3</xdr:col>
       <xdr:colOff>76694</xdr:colOff>
       <xdr:row>25</xdr:row>
-      <xdr:rowOff>3186546</xdr:rowOff>
+      <xdr:rowOff>3287399</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>4121998</xdr:colOff>
       <xdr:row>25</xdr:row>
-      <xdr:rowOff>4807528</xdr:rowOff>
+      <xdr:rowOff>4908381</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -8935,8 +9374,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="23675603" y="47936728"/>
-          <a:ext cx="4051654" cy="1627332"/>
+          <a:off x="25827812" y="47920428"/>
+          <a:ext cx="4045304" cy="1620982"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -8979,8 +9418,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="27845040" y="44938083"/>
-          <a:ext cx="4496021" cy="1878734"/>
+          <a:off x="30389794" y="44820930"/>
+          <a:ext cx="4843403" cy="1878734"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -8992,15 +9431,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>56901</xdr:colOff>
+      <xdr:colOff>79313</xdr:colOff>
       <xdr:row>25</xdr:row>
-      <xdr:rowOff>2397381</xdr:rowOff>
+      <xdr:rowOff>2464616</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>469363</xdr:colOff>
+      <xdr:colOff>491775</xdr:colOff>
       <xdr:row>25</xdr:row>
-      <xdr:rowOff>4952079</xdr:rowOff>
+      <xdr:rowOff>5019314</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -9023,8 +9462,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="27842687" y="47146738"/>
-          <a:ext cx="4222462" cy="2554698"/>
+          <a:off x="30402431" y="47097645"/>
+          <a:ext cx="4569844" cy="2554698"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -9067,7 +9506,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="23665008" y="39742628"/>
+          <a:off x="25828762" y="39623438"/>
           <a:ext cx="1894351" cy="2294371"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -9111,8 +9550,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="25631487" y="39704242"/>
-          <a:ext cx="1618384" cy="2366780"/>
+          <a:off x="27795241" y="39585052"/>
+          <a:ext cx="1624734" cy="2360430"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -9155,8 +9594,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="27319721" y="40241682"/>
-          <a:ext cx="2685610" cy="1111307"/>
+          <a:off x="29483475" y="40122492"/>
+          <a:ext cx="3230623" cy="1111307"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -9243,8 +9682,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="30087445" y="49927081"/>
-          <a:ext cx="5250512" cy="2333419"/>
+          <a:off x="32804871" y="49804750"/>
+          <a:ext cx="5498910" cy="2333419"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -9692,9 +10131,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -9732,7 +10171,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -9838,7 +10277,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -9980,7 +10419,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -9988,18 +10427,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD5EDF3B-973B-45D7-8250-7B4AC099BDCA}">
-  <dimension ref="A1:W34"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <dimension ref="A1:Q34"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="119.453125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="128.7265625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="89.6328125" customWidth="1"/>
+    <col min="1" max="1" width="119.5" style="1" customWidth="1"/>
+    <col min="2" max="2" width="128.75" style="1" customWidth="1"/>
+    <col min="3" max="3" width="89.625" customWidth="1"/>
     <col min="4" max="4" width="60" customWidth="1"/>
-    <col min="5" max="5" width="26.453125" customWidth="1"/>
-    <col min="6" max="6" width="28.08984375" customWidth="1"/>
-    <col min="7" max="7" width="13.08984375" customWidth="1"/>
-    <col min="8" max="8" width="46.7265625" customWidth="1"/>
-    <col min="9" max="9" width="30.81640625" customWidth="1"/>
+    <col min="5" max="5" width="26.5" customWidth="1"/>
+    <col min="6" max="6" width="28.125" customWidth="1"/>
+    <col min="7" max="7" width="13.125" customWidth="1"/>
+    <col min="8" max="8" width="46.75" customWidth="1"/>
+    <col min="9" max="9" width="30.875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="94.5" customHeight="1">
@@ -10010,10 +10449,10 @@
         <v>15</v>
       </c>
       <c r="C1" s="20" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="20.149999999999999" customHeight="1">
+    <row r="2" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A2" s="6" t="s">
         <v>0</v>
       </c>
@@ -10021,82 +10460,82 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="20.149999999999999" customHeight="1">
+    <row r="3" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A3" s="7" t="s">
-        <v>25</v>
+        <v>90</v>
       </c>
       <c r="B3" s="3"/>
     </row>
-    <row r="4" spans="1:8" ht="20.149999999999999" customHeight="1">
+    <row r="4" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A4" s="7" t="s">
-        <v>24</v>
+        <v>91</v>
       </c>
       <c r="B4" s="3"/>
     </row>
-    <row r="5" spans="1:8" ht="20.149999999999999" customHeight="1">
+    <row r="5" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A5" s="7" t="s">
-        <v>23</v>
+        <v>92</v>
       </c>
       <c r="B5" s="3"/>
     </row>
-    <row r="6" spans="1:8" ht="20.149999999999999" customHeight="1">
+    <row r="6" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A6" s="7" t="s">
-        <v>22</v>
+        <v>88</v>
       </c>
       <c r="B6" s="3"/>
     </row>
-    <row r="7" spans="1:8" ht="20.149999999999999" customHeight="1">
+    <row r="7" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A7" s="7" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="B7" s="3"/>
     </row>
-    <row r="8" spans="1:8" ht="20.149999999999999" customHeight="1">
+    <row r="8" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A8" s="7" t="s">
-        <v>26</v>
+        <v>93</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="20.149999999999999" customHeight="1" thickBot="1">
+    <row r="9" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1">
       <c r="A9" s="7" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B9" s="3"/>
     </row>
-    <row r="10" spans="1:8" ht="400" customHeight="1">
-      <c r="A10" s="38" t="s">
+    <row r="10" spans="1:8" ht="399.95" customHeight="1">
+      <c r="A10" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="B10" s="42" t="s">
-        <v>38</v>
+      <c r="B10" s="50" t="s">
+        <v>97</v>
       </c>
-      <c r="C10" s="44" t="s">
-        <v>37</v>
+      <c r="C10" s="52" t="s">
+        <v>96</v>
       </c>
-      <c r="D10" s="45"/>
-      <c r="E10" s="45"/>
+      <c r="D10" s="53"/>
+      <c r="E10" s="53"/>
       <c r="F10" s="27"/>
       <c r="G10" s="27"/>
       <c r="H10" s="28"/>
     </row>
     <row r="11" spans="1:8" ht="120" customHeight="1" thickBot="1">
-      <c r="A11" s="39"/>
-      <c r="B11" s="43"/>
-      <c r="C11" s="46"/>
-      <c r="D11" s="47"/>
-      <c r="E11" s="47"/>
+      <c r="A11" s="49"/>
+      <c r="B11" s="51"/>
+      <c r="C11" s="54"/>
+      <c r="D11" s="55"/>
+      <c r="E11" s="55"/>
       <c r="F11" s="25"/>
       <c r="G11" s="25"/>
       <c r="H11" s="29"/>
     </row>
-    <row r="12" spans="1:8" ht="40" customHeight="1">
+    <row r="12" spans="1:8" ht="39.950000000000003" customHeight="1">
       <c r="A12" s="7" t="s">
         <v>2</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="60" customHeight="1" thickBot="1">
@@ -10112,10 +10551,10 @@
         <v>4</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>29</v>
+        <v>85</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="D14" s="13"/>
       <c r="E14" s="13"/>
@@ -10123,186 +10562,174 @@
       <c r="G14" s="13"/>
       <c r="H14" s="14"/>
     </row>
-    <row r="15" spans="1:8" ht="100" customHeight="1" thickBot="1">
+    <row r="15" spans="1:8" ht="99.95" customHeight="1" thickBot="1">
       <c r="A15" s="7" t="s">
         <v>5</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="340" customHeight="1" thickBot="1">
+    <row r="16" spans="1:8" ht="339.95" customHeight="1" thickBot="1">
       <c r="A16" s="7" t="s">
         <v>6</v>
       </c>
       <c r="B16" s="23" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C16" s="15"/>
       <c r="D16" s="13"/>
       <c r="E16" s="16" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="F16" s="17" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="H16" s="11"/>
     </row>
-    <row r="17" spans="1:23" ht="400" customHeight="1" thickBot="1">
+    <row r="17" spans="1:17" ht="399.95" customHeight="1" thickBot="1">
       <c r="A17" s="7" t="s">
         <v>7</v>
       </c>
       <c r="B17" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="C17" s="40" t="s">
-        <v>36</v>
+      <c r="C17" s="67" t="s">
+        <v>65</v>
       </c>
-      <c r="D17" s="41"/>
+      <c r="D17" s="68"/>
       <c r="E17" s="13"/>
       <c r="F17" s="13"/>
       <c r="G17" s="13"/>
       <c r="H17" s="13"/>
       <c r="I17" s="13"/>
       <c r="J17" s="37"/>
-      <c r="K17" s="90"/>
-      <c r="L17" s="91"/>
-      <c r="M17" s="91"/>
-      <c r="N17" s="91"/>
-      <c r="O17" s="91"/>
-      <c r="P17" s="91"/>
-      <c r="Q17" s="91"/>
-      <c r="R17" s="91"/>
-      <c r="S17" s="91"/>
-      <c r="T17" s="91"/>
-      <c r="U17" s="91"/>
-      <c r="V17" s="91"/>
-      <c r="W17" s="91"/>
+      <c r="K17" s="41"/>
     </row>
-    <row r="18" spans="1:23" ht="20.149999999999999" customHeight="1">
+    <row r="18" spans="1:17" ht="20.100000000000001" customHeight="1">
       <c r="A18" s="7" t="s">
         <v>8</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
     </row>
-    <row r="19" spans="1:23" ht="80" customHeight="1">
+    <row r="19" spans="1:17" ht="80.099999999999994" customHeight="1">
       <c r="A19" s="21" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
     </row>
-    <row r="20" spans="1:23" ht="40" customHeight="1">
+    <row r="20" spans="1:17" ht="39.950000000000003" customHeight="1">
       <c r="A20" s="21" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="B20" s="22" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
     </row>
-    <row r="21" spans="1:23" ht="40" customHeight="1" thickBot="1">
+    <row r="21" spans="1:17" ht="39.950000000000003" customHeight="1" thickBot="1">
       <c r="A21" s="21" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="B21" s="22" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
     </row>
-    <row r="22" spans="1:23" ht="409" customHeight="1" thickBot="1">
+    <row r="22" spans="1:17" ht="408.95" customHeight="1" thickBot="1">
       <c r="A22" s="7" t="s">
         <v>9</v>
       </c>
       <c r="B22" s="23" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="C22" s="26" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="D22" s="13"/>
-      <c r="E22" s="51" t="s">
-        <v>49</v>
+      <c r="E22" s="60" t="s">
+        <v>40</v>
       </c>
-      <c r="F22" s="52"/>
+      <c r="F22" s="61"/>
     </row>
-    <row r="23" spans="1:23" ht="300" customHeight="1" thickBot="1">
+    <row r="23" spans="1:17" ht="300" customHeight="1" thickBot="1">
       <c r="A23" s="7" t="s">
         <v>10</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
-      <c r="C23" s="48" t="s">
-        <v>52</v>
+      <c r="C23" s="57" t="s">
+        <v>43</v>
       </c>
-      <c r="D23" s="49"/>
-      <c r="E23" s="50"/>
+      <c r="D23" s="58"/>
+      <c r="E23" s="59"/>
     </row>
-    <row r="24" spans="1:23" ht="220" customHeight="1" thickBot="1">
+    <row r="24" spans="1:17" ht="219.95" customHeight="1" thickBot="1">
       <c r="A24" s="7" t="s">
         <v>11</v>
       </c>
       <c r="B24" s="23" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="C24" s="30" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="D24" s="19"/>
       <c r="E24" s="19"/>
       <c r="F24" s="31" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="G24" s="27"/>
       <c r="H24" s="17"/>
       <c r="I24" s="24"/>
       <c r="J24" s="24"/>
     </row>
-    <row r="25" spans="1:23" ht="400" customHeight="1">
-      <c r="A25" s="38" t="s">
+    <row r="25" spans="1:17" ht="399.95" customHeight="1">
+      <c r="A25" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="B25" s="42" t="s">
-        <v>41</v>
+      <c r="B25" s="50" t="s">
+        <v>32</v>
       </c>
-      <c r="C25" s="54" t="s">
-        <v>63</v>
+      <c r="C25" s="63" t="s">
+        <v>76</v>
       </c>
       <c r="D25" s="27"/>
       <c r="E25" s="27"/>
       <c r="F25" s="27"/>
       <c r="G25" s="28"/>
     </row>
-    <row r="26" spans="1:23" ht="400" customHeight="1" thickBot="1">
-      <c r="A26" s="39"/>
-      <c r="B26" s="53"/>
-      <c r="C26" s="55"/>
+    <row r="26" spans="1:17" ht="399.95" customHeight="1" thickBot="1">
+      <c r="A26" s="49"/>
+      <c r="B26" s="62"/>
+      <c r="C26" s="64"/>
       <c r="D26" s="32" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
-      <c r="E26" s="56" t="s">
-        <v>57</v>
+      <c r="E26" s="65" t="s">
+        <v>46</v>
       </c>
-      <c r="F26" s="57"/>
+      <c r="F26" s="66"/>
       <c r="G26" s="33"/>
     </row>
-    <row r="27" spans="1:23" ht="200" customHeight="1" thickBot="1">
+    <row r="27" spans="1:17" ht="200.1" customHeight="1" thickBot="1">
       <c r="A27" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="B27" s="59" t="s">
-        <v>61</v>
+      <c r="B27" s="38" t="s">
+        <v>50</v>
       </c>
-      <c r="C27" s="60" t="s">
-        <v>59</v>
+      <c r="C27" s="39" t="s">
+        <v>48</v>
       </c>
-      <c r="D27" s="61" t="s">
-        <v>60</v>
+      <c r="D27" s="56" t="s">
+        <v>49</v>
       </c>
-      <c r="E27" s="61"/>
-      <c r="F27" s="61"/>
+      <c r="E27" s="56"/>
+      <c r="F27" s="56"/>
       <c r="G27" s="27"/>
       <c r="H27" s="27"/>
       <c r="I27" s="27"/>
@@ -10315,100 +10742,100 @@
       <c r="P27" s="36"/>
       <c r="Q27" s="37"/>
     </row>
-    <row r="28" spans="1:23" ht="280" customHeight="1">
-      <c r="A28" s="62" t="s">
-        <v>62</v>
+    <row r="28" spans="1:17" ht="279.95" customHeight="1">
+      <c r="A28" s="81" t="s">
+        <v>51</v>
       </c>
-      <c r="B28" s="63" t="s">
-        <v>40</v>
+      <c r="B28" s="78" t="s">
+        <v>31</v>
       </c>
-      <c r="C28" s="69" t="s">
-        <v>65</v>
+      <c r="C28" s="72" t="s">
+        <v>53</v>
       </c>
       <c r="D28" s="73"/>
-      <c r="E28" s="81"/>
-      <c r="F28" s="82"/>
-      <c r="G28" s="82"/>
-      <c r="H28" s="82"/>
-      <c r="I28" s="83"/>
+      <c r="E28" s="69"/>
+      <c r="F28" s="70"/>
+      <c r="G28" s="70"/>
+      <c r="H28" s="70"/>
+      <c r="I28" s="71"/>
     </row>
-    <row r="29" spans="1:23" ht="220" customHeight="1">
-      <c r="A29" s="64"/>
-      <c r="B29" s="58"/>
-      <c r="C29" s="70" t="s">
-        <v>64</v>
+    <row r="29" spans="1:17" ht="219.95" customHeight="1">
+      <c r="A29" s="82"/>
+      <c r="B29" s="79"/>
+      <c r="C29" s="74" t="s">
+        <v>52</v>
       </c>
-      <c r="D29" s="74"/>
-      <c r="E29" s="77" t="s">
-        <v>66</v>
+      <c r="D29" s="75"/>
+      <c r="E29" s="86" t="s">
+        <v>54</v>
       </c>
-      <c r="F29" s="65"/>
-      <c r="G29" s="65"/>
-      <c r="H29" s="65"/>
-      <c r="I29" s="66"/>
+      <c r="F29" s="87"/>
+      <c r="G29" s="87"/>
+      <c r="H29" s="87"/>
+      <c r="I29" s="88"/>
     </row>
-    <row r="30" spans="1:23" ht="409" customHeight="1">
-      <c r="A30" s="64"/>
-      <c r="B30" s="58"/>
-      <c r="C30" s="70" t="s">
-        <v>68</v>
+    <row r="30" spans="1:17" ht="408.95" customHeight="1">
+      <c r="A30" s="82"/>
+      <c r="B30" s="79"/>
+      <c r="C30" s="74" t="s">
+        <v>56</v>
       </c>
-      <c r="D30" s="74"/>
-      <c r="E30" s="77"/>
-      <c r="F30" s="65"/>
-      <c r="G30" s="65"/>
-      <c r="H30" s="65"/>
-      <c r="I30" s="66"/>
+      <c r="D30" s="75"/>
+      <c r="E30" s="86"/>
+      <c r="F30" s="87"/>
+      <c r="G30" s="87"/>
+      <c r="H30" s="87"/>
+      <c r="I30" s="88"/>
     </row>
-    <row r="31" spans="1:23" ht="280" customHeight="1">
-      <c r="A31" s="64"/>
-      <c r="B31" s="58"/>
-      <c r="C31" s="71" t="s">
-        <v>69</v>
+    <row r="31" spans="1:17" ht="279.95" customHeight="1">
+      <c r="A31" s="82"/>
+      <c r="B31" s="79"/>
+      <c r="C31" s="84" t="s">
+        <v>57</v>
       </c>
-      <c r="D31" s="76"/>
-      <c r="E31" s="78"/>
-      <c r="F31" s="79"/>
-      <c r="G31" s="79"/>
-      <c r="H31" s="79"/>
-      <c r="I31" s="80"/>
+      <c r="D31" s="85"/>
+      <c r="E31" s="89"/>
+      <c r="F31" s="90"/>
+      <c r="G31" s="90"/>
+      <c r="H31" s="90"/>
+      <c r="I31" s="91"/>
     </row>
-    <row r="32" spans="1:23" ht="400" customHeight="1" thickBot="1">
-      <c r="A32" s="67"/>
-      <c r="B32" s="68"/>
-      <c r="C32" s="72" t="s">
-        <v>70</v>
+    <row r="32" spans="1:17" ht="399.95" customHeight="1" thickBot="1">
+      <c r="A32" s="83"/>
+      <c r="B32" s="80"/>
+      <c r="C32" s="76" t="s">
+        <v>58</v>
       </c>
-      <c r="D32" s="75"/>
-      <c r="E32" s="84"/>
-      <c r="F32" s="85"/>
-      <c r="G32" s="85" t="s">
-        <v>67</v>
+      <c r="D32" s="77"/>
+      <c r="E32" s="44"/>
+      <c r="F32" s="42"/>
+      <c r="G32" s="42" t="s">
+        <v>55</v>
       </c>
-      <c r="H32" s="85"/>
-      <c r="I32" s="86"/>
+      <c r="H32" s="42"/>
+      <c r="I32" s="43"/>
     </row>
-    <row r="33" spans="1:12" ht="400" customHeight="1">
+    <row r="33" spans="1:12" ht="399.95" customHeight="1">
       <c r="A33" s="34" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
-      <c r="B33" s="87" t="s">
-        <v>73</v>
+      <c r="B33" s="40" t="s">
+        <v>61</v>
       </c>
-      <c r="C33" s="88"/>
-      <c r="D33" s="89"/>
-      <c r="E33" s="92" t="s">
-        <v>72</v>
+      <c r="C33" s="45"/>
+      <c r="D33" s="46"/>
+      <c r="E33" s="47" t="s">
+        <v>60</v>
       </c>
-      <c r="F33" s="92"/>
-      <c r="G33" s="92"/>
-      <c r="H33" s="92"/>
-      <c r="I33" s="92"/>
-      <c r="J33" s="92"/>
-      <c r="K33" s="92"/>
-      <c r="L33" s="92"/>
+      <c r="F33" s="47"/>
+      <c r="G33" s="47"/>
+      <c r="H33" s="47"/>
+      <c r="I33" s="47"/>
+      <c r="J33" s="47"/>
+      <c r="K33" s="47"/>
+      <c r="L33" s="47"/>
     </row>
-    <row r="34" spans="1:12" ht="20.149999999999999" customHeight="1">
+    <row r="34" spans="1:12" ht="20.100000000000001" customHeight="1">
       <c r="A34" s="8" t="s">
         <v>14</v>
       </c>
@@ -10418,6 +10845,14 @@
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="E29:I31"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="B28:B32"/>
+    <mergeCell ref="A28:A32"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="C31:D31"/>
     <mergeCell ref="G32:I32"/>
     <mergeCell ref="E32:F32"/>
     <mergeCell ref="C33:D33"/>
@@ -10434,17 +10869,166 @@
     <mergeCell ref="E26:F26"/>
     <mergeCell ref="C17:D17"/>
     <mergeCell ref="E28:I28"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="B28:B32"/>
-    <mergeCell ref="A28:A32"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="E29:I31"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D44EA03F-D637-4A56-9F12-1E27AA7DD116}">
+  <dimension ref="A1:B21"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="1" width="30.625" customWidth="1"/>
+    <col min="2" max="2" width="73.125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="99.95" customHeight="1">
+      <c r="A1" s="112" t="s">
+        <v>89</v>
+      </c>
+      <c r="B1" s="113" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="30" customHeight="1">
+      <c r="A2" s="114" t="s">
+        <v>95</v>
+      </c>
+      <c r="B2" s="100" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="30" customHeight="1">
+      <c r="A3" s="115"/>
+      <c r="B3" s="116" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="30" customHeight="1">
+      <c r="A4" s="117" t="s">
+        <v>82</v>
+      </c>
+      <c r="B4" s="92" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="30" customHeight="1">
+      <c r="A5" s="95" t="s">
+        <v>80</v>
+      </c>
+      <c r="B5" s="94" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="30" customHeight="1">
+      <c r="A6" s="108" t="s">
+        <v>63</v>
+      </c>
+      <c r="B6" s="110" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="30" customHeight="1">
+      <c r="A7" s="109"/>
+      <c r="B7" s="111" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="30" customHeight="1">
+      <c r="A8" s="104" t="s">
+        <v>64</v>
+      </c>
+      <c r="B8" s="94"/>
+    </row>
+    <row r="9" spans="1:2" ht="30" customHeight="1">
+      <c r="A9" s="96" t="s">
+        <v>81</v>
+      </c>
+      <c r="B9" s="97" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="30" customHeight="1">
+      <c r="A10" s="96"/>
+      <c r="B10" s="98" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="30" customHeight="1">
+      <c r="A11" s="96"/>
+      <c r="B11" s="99" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="30" customHeight="1">
+      <c r="A12" s="105" t="s">
+        <v>69</v>
+      </c>
+      <c r="B12" s="100" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="30" customHeight="1">
+      <c r="A13" s="93"/>
+      <c r="B13" s="99" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="30" customHeight="1">
+      <c r="A14" s="105" t="s">
+        <v>74</v>
+      </c>
+      <c r="B14" s="97" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="30" customHeight="1">
+      <c r="A15" s="93"/>
+      <c r="B15" s="99" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="30" customHeight="1">
+      <c r="A16" s="105" t="s">
+        <v>77</v>
+      </c>
+      <c r="B16" s="97" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="30" customHeight="1">
+      <c r="A17" s="93"/>
+      <c r="B17" s="101" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="30" customHeight="1">
+      <c r="A18" s="106" t="s">
+        <v>83</v>
+      </c>
+      <c r="B18" s="107" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="30" customHeight="1">
+      <c r="A19" s="102"/>
+      <c r="B19" s="103"/>
+    </row>
+    <row r="20" spans="1:2" ht="30" customHeight="1"/>
+    <row r="21" spans="1:2" ht="30" customHeight="1"/>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="A9:A11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="A6:A7"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>